--- a/artfynd/A 1101-2024 artfynd.xlsx
+++ b/artfynd/A 1101-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1101-2024 artfynd.xlsx
+++ b/artfynd/A 1101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,6 +1457,122 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121631194</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56257</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gävle Kringlan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>613195</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6745009</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Andreas Mitander</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jeanette Karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1101-2024 artfynd.xlsx
+++ b/artfynd/A 1101-2024 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>121631194</v>
       </c>
       <c r="B9" t="n">
-        <v>56257</v>
+        <v>56258</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 1101-2024 artfynd.xlsx
+++ b/artfynd/A 1101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81769850</v>
+        <v>81769955</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613023.9185163716</v>
+        <v>612987</v>
       </c>
       <c r="R2" t="n">
-        <v>6745052.013955726</v>
+        <v>6745073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81770323</v>
+        <v>81770314</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613204.1107019804</v>
+        <v>613186</v>
       </c>
       <c r="R3" t="n">
-        <v>6745058.216591442</v>
+        <v>6745151</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Hille</t>
+          <t>Hamrånge</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -860,19 +840,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81769955</v>
+        <v>81770315</v>
       </c>
       <c r="B4" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612987.0842223198</v>
+        <v>613108</v>
       </c>
       <c r="R4" t="n">
-        <v>6745072.810297673</v>
+        <v>6745128</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +929,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Hille</t>
+          <t>Hamrånge</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -972,19 +937,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>81769965</v>
+        <v>81770318</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613213.1042081781</v>
+        <v>612975</v>
       </c>
       <c r="R5" t="n">
-        <v>6745082.905846022</v>
+        <v>6745108</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1026,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Hille</t>
+          <t>Hamrånge</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1084,19 +1034,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>81770050</v>
+        <v>81770319</v>
       </c>
       <c r="B6" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613095.9805015896</v>
+        <v>613085</v>
       </c>
       <c r="R6" t="n">
-        <v>6745061.131285152</v>
+        <v>6745081</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,16 +1163,11 @@
         <v>81770322</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613285.9683855033</v>
+        <v>613286</v>
       </c>
       <c r="R7" t="n">
-        <v>6745005.174282284</v>
+        <v>6745005</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,19 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>81770319</v>
+        <v>81770323</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613085.0909686468</v>
+        <v>613204</v>
       </c>
       <c r="R8" t="n">
-        <v>6745080.797070602</v>
+        <v>6745058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2019-09-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-09-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,59 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121631194</v>
+        <v>81770050</v>
       </c>
       <c r="B9" t="n">
-        <v>56266</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gävle Kringlan, Gstr</t>
+          <t>Gävle-Kringlan, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613195</v>
+        <v>613096</v>
       </c>
       <c r="R9" t="n">
-        <v>6745009</v>
+        <v>6745061</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-26</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,24 +1435,324 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Andreas Mitander</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Barbara Kühn, Kajsa Mattsson, Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>81769850</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gävle-Kringlan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>613024</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6745052</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Barbara Kühn, Kajsa Mattsson, Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>81769965</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gävle-Kringlan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>613213</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6745083</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-09-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Barbara Kühn</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Barbara Kühn, Kajsa Mattsson, Anna Broberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121631194</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gävle Kringlan, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>613195</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6745009</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Andreas Mitander</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Jeanette Karlsson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Jeanette Karlsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1101-2024 artfynd.xlsx
+++ b/artfynd/A 1101-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81769955</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770314</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770315</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770319</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770322</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770323</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81770050</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81769850</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81769965</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,8 +1808,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121631194</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>